--- a/states.xlsx
+++ b/states.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z52"/>
+  <dimension ref="A1:AA52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -606,6 +606,11 @@
           <t>State Hub Published</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Climate Hazards</t>
+        </is>
+      </c>
     </row>
     <row r="2" hidden="1" ht="28.8" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -718,6 +723,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Tornado, Hurricane, Severe Thunderstorm</t>
+        </is>
+      </c>
     </row>
     <row r="3" hidden="1" ht="28.8" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -830,6 +840,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Extreme Cold, Earthquake, High Wind</t>
+        </is>
+      </c>
     </row>
     <row r="4" hidden="1" ht="28.8" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -942,6 +957,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Extreme Heat, Dust Storm, Wildfire</t>
+        </is>
+      </c>
     </row>
     <row r="5" hidden="1" ht="28.8" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -1054,6 +1074,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Tornado, Severe Thunderstorm, Ice Storm</t>
+        </is>
+      </c>
     </row>
     <row r="6" hidden="1" ht="28.8" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -1166,6 +1191,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Wildfire, Earthquake, Extreme Heat</t>
+        </is>
+      </c>
     </row>
     <row r="7" hidden="1" ht="28.8" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -1278,6 +1308,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Hail, Wildfire, Blizzard</t>
+        </is>
+      </c>
     </row>
     <row r="8" hidden="1" ht="28.8" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1390,6 +1425,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Nor'easter, Ice Storm, Severe Thunderstorm</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="28.8" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -1502,6 +1542,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Nor'easter, Coastal Flooding, Severe Thunderstorm</t>
+        </is>
+      </c>
     </row>
     <row r="10" hidden="1" ht="28.8" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1614,6 +1659,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Severe Thunderstorm, Extreme Heat, Ice Storm</t>
+        </is>
+      </c>
     </row>
     <row r="11" hidden="1" ht="28.8" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -1726,6 +1776,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Hurricane, Severe Thunderstorm, Flooding</t>
+        </is>
+      </c>
     </row>
     <row r="12" hidden="1" ht="28.8" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -1838,6 +1893,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Tornado, Hurricane, Ice Storm</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="28.8" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -1950,6 +2010,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Tropical Storm, Volcanic Activity, Flooding</t>
+        </is>
+      </c>
     </row>
     <row r="14" hidden="1" ht="28.8" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -2062,6 +2127,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Wildfire, Extreme Cold, Winter Storm</t>
+        </is>
+      </c>
     </row>
     <row r="15" hidden="1" ht="28.8" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -2174,6 +2244,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Tornado, Extreme Cold, Severe Thunderstorm</t>
+        </is>
+      </c>
     </row>
     <row r="16" hidden="1" ht="28.8" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -2286,6 +2361,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Tornado, Severe Thunderstorm, Ice Storm</t>
+        </is>
+      </c>
     </row>
     <row r="17" hidden="1" ht="28.8" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -2398,6 +2478,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Tornado, Severe Thunderstorm, Blizzard</t>
+        </is>
+      </c>
     </row>
     <row r="18" hidden="1" ht="28.8" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -2510,6 +2595,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Tornado, Hail, Severe Thunderstorm</t>
+        </is>
+      </c>
     </row>
     <row r="19" hidden="1" ht="28.8" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -2622,6 +2712,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Tornado, Ice Storm, Severe Thunderstorm</t>
+        </is>
+      </c>
     </row>
     <row r="20" hidden="1" ht="28.8" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -2734,6 +2829,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Hurricane, Flooding, Tornado</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="28.8" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -2846,6 +2946,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Nor'easter, Ice Storm, Extreme Cold</t>
+        </is>
+      </c>
     </row>
     <row r="22" hidden="1" ht="43.2" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -2958,6 +3063,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Nor'easter, Severe Thunderstorm, Hurricane</t>
+        </is>
+      </c>
     </row>
     <row r="23" hidden="1" ht="28.8" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -3070,6 +3180,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Nor'easter, Blizzard, Coastal Flooding</t>
+        </is>
+      </c>
     </row>
     <row r="24" hidden="1" ht="28.8" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -3182,6 +3297,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Lake-Effect Snow, Extreme Cold, Severe Thunderstorm</t>
+        </is>
+      </c>
     </row>
     <row r="25" hidden="1" ht="28.8" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -3294,6 +3414,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Extreme Cold, Blizzard, Tornado</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="28.8" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -3406,6 +3531,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Tornado, Hurricane, Severe Thunderstorm</t>
+        </is>
+      </c>
     </row>
     <row r="27" hidden="1" ht="28.8" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -3518,6 +3648,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Tornado, Severe Thunderstorm, Ice Storm</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="28.8" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -3630,6 +3765,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Wildfire, Winter Storm, Extreme Cold</t>
+        </is>
+      </c>
     </row>
     <row r="29" hidden="1" ht="28.8" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
@@ -3742,6 +3882,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Tornado, Blizzard, Hail</t>
+        </is>
+      </c>
     </row>
     <row r="30" hidden="1" ht="28.8" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -3854,6 +3999,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Wildfire, Extreme Heat, Earthquake</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="28.8" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
@@ -3966,6 +4116,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Nor'easter, Ice Storm, Extreme Cold</t>
+        </is>
+      </c>
     </row>
     <row r="32" hidden="1" ht="28.8" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -4078,6 +4233,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Nor'easter, Coastal Flooding, Hurricane</t>
+        </is>
+      </c>
     </row>
     <row r="33" hidden="1" ht="28.8" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
@@ -4190,6 +4350,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Wildfire, Severe Thunderstorm, Extreme Heat</t>
+        </is>
+      </c>
     </row>
     <row r="34" hidden="1" ht="28.8" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -4302,6 +4467,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Nor'easter, Lake-Effect Snow, Ice Storm</t>
+        </is>
+      </c>
     </row>
     <row r="35" hidden="1" ht="28.8" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
@@ -4414,6 +4584,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Hurricane, Tornado, Ice Storm</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="28.8" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -4526,6 +4701,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Extreme Cold, Blizzard, Tornado</t>
+        </is>
+      </c>
     </row>
     <row r="37" hidden="1" ht="28.8" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
@@ -4638,6 +4818,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Tornado, Lake-Effect Snow, Ice Storm</t>
+        </is>
+      </c>
     </row>
     <row r="38" hidden="1">
       <c r="A38" s="2" t="inlineStr">
@@ -4750,6 +4935,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>Tornado, Severe Thunderstorm, Ice Storm</t>
+        </is>
+      </c>
     </row>
     <row r="39" hidden="1" ht="28.8" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
@@ -4862,6 +5052,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>Wildfire, Earthquake, Winter Storm</t>
+        </is>
+      </c>
     </row>
     <row r="40" hidden="1" ht="28.8" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -4974,6 +5169,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>Ice Storm, Nor'easter, Severe Thunderstorm</t>
+        </is>
+      </c>
     </row>
     <row r="41" hidden="1" ht="28.8" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
@@ -5086,6 +5286,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Nor'easter, Coastal Flooding, Ice Storm</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="28.8" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -5198,6 +5403,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>Hurricane, Tornado, Ice Storm</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="28.8" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
@@ -5310,6 +5520,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Blizzard, Tornado, Hail</t>
+        </is>
+      </c>
     </row>
     <row r="44" hidden="1" ht="28.8" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -5422,6 +5637,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>Tornado, Ice Storm, Severe Thunderstorm</t>
+        </is>
+      </c>
     </row>
     <row r="45" hidden="1" ht="28.8" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
@@ -5534,6 +5754,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>Hurricane, Tornado, Extreme Heat</t>
+        </is>
+      </c>
     </row>
     <row r="46" hidden="1" ht="28.8" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -5646,6 +5871,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Wildfire, Earthquake, Winter Storm</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="28.8" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
@@ -5758,6 +5988,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>Nor'easter, Ice Storm, Extreme Cold</t>
+        </is>
+      </c>
     </row>
     <row r="48" hidden="1" ht="28.8" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
@@ -5870,6 +6105,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>Hurricane, Tornado, Ice Storm</t>
+        </is>
+      </c>
     </row>
     <row r="49" hidden="1" ht="28.8" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
@@ -5982,6 +6222,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>Wildfire, Earthquake, Winter Storm</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="28.8" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
@@ -6094,6 +6339,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>Ice Storm, Severe Thunderstorm, Flooding</t>
+        </is>
+      </c>
     </row>
     <row r="51" hidden="1" ht="28.8" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
@@ -6206,6 +6456,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>Extreme Cold, Lake-Effect Snow, Tornado</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="28.8" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -6316,6 +6571,11 @@
       <c r="Z52" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>Winter Storm, Extreme Cold, Wildfire</t>
         </is>
       </c>
     </row>

--- a/states.xlsx
+++ b/states.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA52"/>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -611,6 +611,16 @@
           <t>Climate Hazards</t>
         </is>
       </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>State Energy Office Name</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>State Energy Office URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" hidden="1" ht="28.8" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -728,6 +738,16 @@
           <t>Tornado, Hurricane, Severe Thunderstorm</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Alabama Department of Economic and Community Affairs</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>https://adeca.alabama.gov/energy/</t>
+        </is>
+      </c>
     </row>
     <row r="3" hidden="1" ht="28.8" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -845,6 +865,16 @@
           <t>Extreme Cold, Earthquake, High Wind</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Alaska Energy Authority</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>https://www.akenergyauthority.org</t>
+        </is>
+      </c>
     </row>
     <row r="4" hidden="1" ht="28.8" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -962,6 +992,16 @@
           <t>Extreme Heat, Dust Storm, Wildfire</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Office of Resiliency, Arizona Executive Office of the Governor</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>https://resilient.az.gov</t>
+        </is>
+      </c>
     </row>
     <row r="5" hidden="1" ht="28.8" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -1079,6 +1119,16 @@
           <t>Tornado, Severe Thunderstorm, Ice Storm</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Energy Office, Arkansas Department of Energy and Environment</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>https://www.adeq.state.ar.us</t>
+        </is>
+      </c>
     </row>
     <row r="6" hidden="1" ht="28.8" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -1196,6 +1246,16 @@
           <t>Wildfire, Earthquake, Extreme Heat</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>California Energy Commission</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>https://www.energy.ca.gov</t>
+        </is>
+      </c>
     </row>
     <row r="7" hidden="1" ht="28.8" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -1313,6 +1373,16 @@
           <t>Hail, Wildfire, Blizzard</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Colorado Energy Office</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>https://energyoffice.colorado.gov</t>
+        </is>
+      </c>
     </row>
     <row r="8" hidden="1" ht="28.8" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1430,6 +1500,16 @@
           <t>Nor'easter, Ice Storm, Severe Thunderstorm</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Connecticut Department of Energy and Environmental Protection</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>https://portal.ct.gov/DEEP</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="28.8" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -1547,6 +1627,16 @@
           <t>Nor'easter, Coastal Flooding, Severe Thunderstorm</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Division of Climate, Coastal, and Energy, Delaware Department of Natural Resources and Environmental Control</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>https://dnrec.alpha.delaware.gov/climate-coastal-energy/</t>
+        </is>
+      </c>
     </row>
     <row r="10" hidden="1" ht="28.8" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1664,6 +1754,16 @@
           <t>Severe Thunderstorm, Extreme Heat, Ice Storm</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>District Department of Energy and Environment</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>https://doee.dc.gov</t>
+        </is>
+      </c>
     </row>
     <row r="11" hidden="1" ht="28.8" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -1781,6 +1881,16 @@
           <t>Hurricane, Severe Thunderstorm, Flooding</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Office of Energy, Florida Department of Agriculture and Consumer Services</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>https://www.fdacs.gov/Divisions-Offices/Energy</t>
+        </is>
+      </c>
     </row>
     <row r="12" hidden="1" ht="28.8" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -1898,6 +2008,16 @@
           <t>Tornado, Hurricane, Ice Storm</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Energy Resources Division, Georgia Environmental Finance Authority</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>https://gefa.georgia.gov</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="28.8" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -2015,6 +2135,16 @@
           <t>Tropical Storm, Volcanic Activity, Flooding</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Hawaii State Energy Office</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>https://energy.hawaii.gov</t>
+        </is>
+      </c>
     </row>
     <row r="14" hidden="1" ht="28.8" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -2132,6 +2262,16 @@
           <t>Wildfire, Extreme Cold, Winter Storm</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Idaho Governor's Office of Energy and Mineral Resources</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>https://oemr.idaho.gov</t>
+        </is>
+      </c>
     </row>
     <row r="15" hidden="1" ht="28.8" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -2249,6 +2389,16 @@
           <t>Tornado, Extreme Cold, Severe Thunderstorm</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Illinois Environmental Protection Agency</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>https://epa.illinois.gov</t>
+        </is>
+      </c>
     </row>
     <row r="16" hidden="1" ht="28.8" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -2366,6 +2516,16 @@
           <t>Tornado, Severe Thunderstorm, Ice Storm</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Indiana Office of Energy Development</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>https://www.in.gov/oed</t>
+        </is>
+      </c>
     </row>
     <row r="17" hidden="1" ht="28.8" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -2483,6 +2643,16 @@
           <t>Tornado, Severe Thunderstorm, Blizzard</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Iowa Economic Development Authority Energy Office</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>https://opportunityiowa.gov/community/energy</t>
+        </is>
+      </c>
     </row>
     <row r="18" hidden="1" ht="28.8" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -2600,6 +2770,16 @@
           <t>Tornado, Hail, Severe Thunderstorm</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Kansas Energy Office, Kansas Corporation Commission</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>https://kcc.ks.gov</t>
+        </is>
+      </c>
     </row>
     <row r="19" hidden="1" ht="28.8" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -2717,6 +2897,16 @@
           <t>Tornado, Ice Storm, Severe Thunderstorm</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Kentucky Office of Energy Policy</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>https://eec.ky.gov/Energy/Pages/default.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="20" hidden="1" ht="28.8" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -2834,6 +3024,16 @@
           <t>Hurricane, Flooding, Tornado</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Louisiana Department of Conservation and Energy</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>https://www.dce.louisiana.gov</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="28.8" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -2951,6 +3151,16 @@
           <t>Nor'easter, Ice Storm, Extreme Cold</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Maine Governor's Energy Office</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>https://www.maine.gov/energy/</t>
+        </is>
+      </c>
     </row>
     <row r="22" hidden="1" ht="43.2" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -3068,6 +3278,16 @@
           <t>Nor'easter, Severe Thunderstorm, Hurricane</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Maryland Energy Administration</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>https://energy.maryland.gov</t>
+        </is>
+      </c>
     </row>
     <row r="23" hidden="1" ht="28.8" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -3185,6 +3405,16 @@
           <t>Nor'easter, Blizzard, Coastal Flooding</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Massachusetts Department of Energy Resources</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>https://www.mass.gov/doer/</t>
+        </is>
+      </c>
     </row>
     <row r="24" hidden="1" ht="28.8" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -3302,6 +3532,16 @@
           <t>Lake-Effect Snow, Extreme Cold, Severe Thunderstorm</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Michigan Department of Environment, Great Lakes, and Energy</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>https://www.michigan.gov/egle/</t>
+        </is>
+      </c>
     </row>
     <row r="25" hidden="1" ht="28.8" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -3419,6 +3659,16 @@
           <t>Extreme Cold, Blizzard, Tornado</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>Energy Division, Minnesota Department of Commerce</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>https://mn.gov/commerce/energy/</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="28.8" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -3536,6 +3786,16 @@
           <t>Tornado, Hurricane, Severe Thunderstorm</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>Energy and Natural Resources Division, Mississippi Development Authority</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>https://mississippi.org/community-resources/office-of-energy/</t>
+        </is>
+      </c>
     </row>
     <row r="27" hidden="1" ht="28.8" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -3653,6 +3913,16 @@
           <t>Tornado, Severe Thunderstorm, Ice Storm</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>Division of Energy, Missouri Department of Natural Resources</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>https://dnr.mo.gov/energy</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="28.8" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -3770,6 +4040,16 @@
           <t>Wildfire, Winter Storm, Extreme Cold</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>Montana Department of Environmental Quality</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>https://deq.mt.gov/energy/</t>
+        </is>
+      </c>
     </row>
     <row r="29" hidden="1" ht="28.8" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
@@ -3887,6 +4167,16 @@
           <t>Tornado, Blizzard, Hail</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>Nebraska Department of Water, Energy, and Environment</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>https://dwee.nebraska.gov/</t>
+        </is>
+      </c>
     </row>
     <row r="30" hidden="1" ht="28.8" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -4004,6 +4294,16 @@
           <t>Wildfire, Extreme Heat, Earthquake</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Nevada Governor's Office of Energy</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>https://www.energy.nv.gov/</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="28.8" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
@@ -4121,6 +4421,16 @@
           <t>Nor'easter, Ice Storm, Extreme Cold</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>New Hampshire Department of Energy</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>https://www.energy.nh.gov/</t>
+        </is>
+      </c>
     </row>
     <row r="32" hidden="1" ht="28.8" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -4238,6 +4548,16 @@
           <t>Nor'easter, Coastal Flooding, Hurricane</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>New Jersey Board of Public Utilities</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>https://www.nj.gov/bpu/bpu/about/divisions/energy/</t>
+        </is>
+      </c>
     </row>
     <row r="33" hidden="1" ht="28.8" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
@@ -4355,6 +4675,16 @@
           <t>Wildfire, Severe Thunderstorm, Extreme Heat</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>Energy Conservation and Management Division, New Mexico Energy, Minerals and Natural Resources Department</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>https://www.emnrd.nm.gov/ecmd/</t>
+        </is>
+      </c>
     </row>
     <row r="34" hidden="1" ht="28.8" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -4472,6 +4802,16 @@
           <t>Nor'easter, Lake-Effect Snow, Ice Storm</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>New York State Energy Research and Development Authority</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>https://nyserda.ny.gov</t>
+        </is>
+      </c>
     </row>
     <row r="35" hidden="1" ht="28.8" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
@@ -4589,6 +4929,16 @@
           <t>Hurricane, Tornado, Ice Storm</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>North Carolina Department of Environmental Quality State Energy Office</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>https://www.deq.nc.gov/energy-climate/state-energy-office</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="28.8" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -4706,6 +5056,16 @@
           <t>Extreme Cold, Blizzard, Tornado</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>Division of Community Services, North Dakota Department of Commerce</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>https://www.commerce.nd.gov/</t>
+        </is>
+      </c>
     </row>
     <row r="37" hidden="1" ht="28.8" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
@@ -4823,6 +5183,16 @@
           <t>Tornado, Lake-Effect Snow, Ice Storm</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Ohio Department of Development</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>https://development.ohio.gov</t>
+        </is>
+      </c>
     </row>
     <row r="38" hidden="1">
       <c r="A38" s="2" t="inlineStr">
@@ -4940,6 +5310,16 @@
           <t>Tornado, Severe Thunderstorm, Ice Storm</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>Oklahoma Secretary of Energy and Environment</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>https://ee.ok.gov/what-we-do/state-energy-office/</t>
+        </is>
+      </c>
     </row>
     <row r="39" hidden="1" ht="28.8" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
@@ -5057,6 +5437,16 @@
           <t>Wildfire, Earthquake, Winter Storm</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Oregon Department of Energy</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>https://www.oregon.gov/energy</t>
+        </is>
+      </c>
     </row>
     <row r="40" hidden="1" ht="28.8" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -5174,6 +5564,16 @@
           <t>Ice Storm, Nor'easter, Severe Thunderstorm</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Energy Programs Office, Pennsylvania Department of Environmental Protection</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/agencies/dep/programs-and-services/energy-programs-office</t>
+        </is>
+      </c>
     </row>
     <row r="41" hidden="1" ht="28.8" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
@@ -5291,6 +5691,16 @@
           <t>Nor'easter, Coastal Flooding, Ice Storm</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>Rhode Island Office of Energy Resources</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>https://energy.ri.gov</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="28.8" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -5408,6 +5818,16 @@
           <t>Hurricane, Tornado, Ice Storm</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>South Carolina Energy Office, Office of Regulatory Staff</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>https://energy.sc.gov</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="28.8" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
@@ -5525,6 +5945,16 @@
           <t>Blizzard, Tornado, Hail</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>Energy Management Office, South Dakota Bureau of Administration</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>https://boa.sd.gov/state-engineer/energy-management.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="44" hidden="1" ht="28.8" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -5642,6 +6072,16 @@
           <t>Tornado, Ice Storm, Severe Thunderstorm</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>Office of Energy Programs, Tennessee Department of Environment and Conservation</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>https://www.tn.gov/environment/program-areas/energy.html</t>
+        </is>
+      </c>
     </row>
     <row r="45" hidden="1" ht="28.8" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
@@ -5759,6 +6199,16 @@
           <t>Hurricane, Tornado, Extreme Heat</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>State Energy Conservation Office, Texas Comptroller of Public Accounts</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>https://seco.cpa.texas.gov</t>
+        </is>
+      </c>
     </row>
     <row r="46" hidden="1" ht="28.8" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -5876,6 +6326,16 @@
           <t>Wildfire, Earthquake, Winter Storm</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>Utah Office of Energy Development</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>https://energy.utah.gov</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="28.8" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
@@ -5993,6 +6453,16 @@
           <t>Nor'easter, Ice Storm, Extreme Cold</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>Planning and Energy Resources Division, Vermont Department of Public Service</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>https://publicservice.vermont.gov/about-us/divisions</t>
+        </is>
+      </c>
     </row>
     <row r="48" hidden="1" ht="28.8" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
@@ -6110,6 +6580,16 @@
           <t>Hurricane, Tornado, Ice Storm</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Virginia Department of Energy</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>https://energy.virginia.gov</t>
+        </is>
+      </c>
     </row>
     <row r="49" hidden="1" ht="28.8" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
@@ -6227,6 +6707,16 @@
           <t>Wildfire, Earthquake, Winter Storm</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>Washington State Department of Commerce Energy Division</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>https://www.commerce.wa.gov/energy/</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="28.8" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
@@ -6344,6 +6834,16 @@
           <t>Ice Storm, Severe Thunderstorm, Flooding</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>West Virginia Office of Energy</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>https://www.energywv.org</t>
+        </is>
+      </c>
     </row>
     <row r="51" hidden="1" ht="28.8" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
@@ -6461,6 +6961,16 @@
           <t>Extreme Cold, Lake-Effect Snow, Tornado</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Office of Energy Innovation, Public Service Commission of Wisconsin</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>https://psc.wi.gov/Pages/ServiceType/OfficeEnergyInnovation.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="28.8" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -6576,6 +7086,16 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>Winter Storm, Extreme Cold, Wildfire</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Wyoming Energy Authority</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>https://www.wyoenergy.org/</t>
         </is>
       </c>
     </row>

--- a/states.xlsx
+++ b/states.xlsx
@@ -5185,12 +5185,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Ohio Department of Development</t>
+          <t>U.S. DOE State Energy Program (Ohio administered by the Ohio Department of Development)</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>https://development.ohio.gov</t>
+          <t>https://www.energy.gov/cmei/scep/about-state-energy-program</t>
         </is>
       </c>
     </row>

--- a/states.xlsx
+++ b/states.xlsx
@@ -5185,12 +5185,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>U.S. DOE State Energy Program (Ohio administered by the Ohio Department of Development)</t>
+          <t>U.S. Department of Energy</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>https://www.energy.gov/cmei/scep/about-state-energy-program</t>
+          <t>https://www.energy.gov/</t>
         </is>
       </c>
     </row>

--- a/states.xlsx
+++ b/states.xlsx
@@ -5127,7 +5127,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>https://elicense4.com.ohio.gov/lookup/licenselookup.aspx</t>
+          <t>https://elicense.ohio.gov/oh_verifylicense</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
